--- a/CZR.xlsx
+++ b/CZR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CECC497-F753-48C7-9084-1BC6BDC91730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFCFFD3-AE98-4D02-98E9-D4757A14EBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="13170" windowHeight="15585" activeTab="1" xr2:uid="{9627131F-423F-4F60-B94E-6A88522ED2E4}"/>
   </bookViews>
